--- a/SRC_Q&A/Q&A.xlsx
+++ b/SRC_Q&A/Q&A.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eclipse1\SoftwareTesting_Nhom22_2024\SRC_Q&amp;A\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Q&amp;A" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Cảm ơn đề xuất của bạn. Chúng nhận thấy đây cũng là một đề xuất giúp phát triển hệ thống, chúng tôi sẽ cân nhắc và xem xét thực hiện đề xuất này.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       </t>
   </si>
 </sst>
 </file>
@@ -223,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -246,11 +249,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -279,6 +302,14 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -499,7 +530,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -607,7 +638,7 @@
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
     </row>
-    <row r="3" spans="1:15" ht="165.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -730,7 +761,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -812,7 +843,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
@@ -853,7 +884,7 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>45</v>
       </c>
@@ -975,6 +1006,17 @@
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="9"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F13" s="10" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
